--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T11:43:27+00:00</t>
+    <t>2026-07-01T12:03:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T12:03:19+00:00</t>
+    <t>2026-07-03T07:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -723,7 +723,7 @@
     <t>The title (eg "My Tasks", "Outstanding Tasks for Patient X") should go into the code.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-mode-de-transport-cisis|20260420150251</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-mode-de-transport-cisis|20260619134043</t>
   </si>
   <si>
     <t>Request.code, Event.code</t>
@@ -1450,7 +1450,7 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis|202604200000</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis|202606190000</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -1598,7 +1598,7 @@
     <t>Task.input:typeMotorisation.value[x]</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-motorisation-cisis|20260420150250</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-motorisation-cisis|20260619134042</t>
   </si>
   <si>
     <t>Task.input:natureTransport</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T07:33:59+00:00</t>
+    <t>2026-07-08T09:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-task-patient-transport-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T09:43:12+00:00</t>
+    <t>2026-07-08T10:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
